--- a/slots/resources/sample/SpecialAuxiliaryAward.xlsx
+++ b/slots/resources/sample/SpecialAuxiliaryAward.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D20924-073D-457C-ADC2-25DB66ACF43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBE89C3-5D99-413C-BA75-5DC4F734BB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -624,9 +624,6 @@
     <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP4&amp;100100004,1,1</t>
   </si>
   <si>
-    <t>4&amp;0,2,1;4&amp;10,4,1;4&amp;12,3,1;4&amp;14,2,1;4&amp;16,2,1;4&amp;18,1,1;4&amp;20,1,1;4&amp;22,1,1;4&amp;24,1,1;4&amp;26,1,1;4&amp;28,1,1;4&amp;30,1,1;JP4,100100004,1,1</t>
-  </si>
-  <si>
     <t>4&amp;10,4,1;4&amp;12,3,1;4&amp;14,2,1;4&amp;16,2,1;4&amp;18,1,1;4&amp;20,1,1;4&amp;22,1,1;4&amp;24,1,1;4&amp;26,1,1;4&amp;28,1,1;4&amp;30,1,1;JP4&amp;100100004,1,1</t>
   </si>
   <si>
@@ -659,6 +656,10 @@
   </si>
   <si>
     <t>3,1,1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>4&amp;0,2,1;4&amp;10,4,1;4&amp;12,3,1;4&amp;14,2,1;4&amp;16,2,1;4&amp;18,1,1;4&amp;20,1,1;4&amp;22,1,1;4&amp;24,1,1;4&amp;26,1,1;4&amp;28,1,1;4&amp;30,1,1;JP4&amp;100100004,1,1</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -667,8 +668,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0_ "/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -802,17 +803,17 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1157,7 +1158,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
@@ -1314,7 +1315,7 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>15</v>
@@ -1337,7 +1338,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>15</v>
@@ -1360,7 +1361,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>16</v>
@@ -1378,7 +1379,7 @@
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -1398,7 +1399,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -1418,7 +1419,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -1438,7 +1439,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -1458,7 +1459,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -1478,7 +1479,7 @@
         <v>19</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1498,7 +1499,7 @@
         <v>6</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>

--- a/slots/resources/sample/SpecialAuxiliaryAward.xlsx
+++ b/slots/resources/sample/SpecialAuxiliaryAward.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBE89C3-5D99-413C-BA75-5DC4F734BB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E1D7CB-9368-4AA5-9E07-CB10AF9754EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -387,7 +387,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="87">
   <si>
     <t>辅助ID</t>
   </si>
@@ -660,6 +660,10 @@
   </si>
   <si>
     <t>4&amp;0,2,1;4&amp;10,4,1;4&amp;12,3,1;4&amp;14,2,1;4&amp;16,2,1;4&amp;18,1,1;4&amp;20,1,1;4&amp;22,1,1;4&amp;24,1,1;4&amp;26,1,1;4&amp;28,1,1;4&amp;30,1,1;JP4&amp;100100004,1,1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>10010009,1,1</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -1105,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.75" customWidth="1"/>
@@ -1430,36 +1434,34 @@
     </row>
     <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>1001000801</v>
+        <v>1001000703</v>
       </c>
       <c r="B15" s="1">
         <v>100100</v>
       </c>
       <c r="C15" s="1">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G15" s="1"/>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>1001000802</v>
+        <v>1001000801</v>
       </c>
       <c r="B16" s="1">
         <v>100100</v>
       </c>
       <c r="C16" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -1470,47 +1472,67 @@
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>1001000901</v>
+        <v>1001000802</v>
       </c>
       <c r="B17" s="1">
         <v>100100</v>
       </c>
       <c r="C17" s="1">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>1001000902</v>
+        <v>1001000901</v>
       </c>
       <c r="B18" s="1">
         <v>100100</v>
       </c>
       <c r="C18" s="1">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>1001000902</v>
+      </c>
+      <c r="B19" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C19" s="1">
+        <v>6</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="H19" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="A1:G4 D5:D11 E5:E18">
+  <conditionalFormatting sqref="A1:G4 D5:D11 E5:E19">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(MID($A1,1,4),2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/SpecialAuxiliaryAward.xlsx
+++ b/slots/resources/sample/SpecialAuxiliaryAward.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E1D7CB-9368-4AA5-9E07-CB10AF9754EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB77A7A-4FA5-4B66-A102-3BC89687D037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -612,21 +612,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP1&amp;100100001,1,1</t>
-  </si>
-  <si>
-    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP2&amp;100100002,1,1</t>
-  </si>
-  <si>
-    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP3&amp;100100003,1,1</t>
-  </si>
-  <si>
-    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP4&amp;100100004,1,1</t>
-  </si>
-  <si>
-    <t>4&amp;10,4,1;4&amp;12,3,1;4&amp;14,2,1;4&amp;16,2,1;4&amp;18,1,1;4&amp;20,1,1;4&amp;22,1,1;4&amp;24,1,1;4&amp;26,1,1;4&amp;28,1,1;4&amp;30,1,1;JP4&amp;100100004,1,1</t>
-  </si>
-  <si>
     <t>2,1,1;3,1,1;4,1,1;5,1,1;6,1,1;7,1,1;8,1,1;9,1,1;10,1,1</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -659,11 +644,31 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>4&amp;0,2,1;4&amp;10,4,1;4&amp;12,3,1;4&amp;14,2,1;4&amp;16,2,1;4&amp;18,1,1;4&amp;20,1,1;4&amp;22,1,1;4&amp;24,1,1;4&amp;26,1,1;4&amp;28,1,1;4&amp;30,1,1;JP4&amp;100100004,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>10010009,1,1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP1&amp;100100101,1,1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP2&amp;100100102,1,1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP3&amp;100100103,1,1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP4&amp;100100104,1,1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>4&amp;0,2,1;4&amp;10,4,1;4&amp;12,3,1;4&amp;14,2,1;4&amp;16,2,1;4&amp;18,1,1;4&amp;20,1,1;4&amp;22,1,1;4&amp;24,1,1;4&amp;26,1,1;4&amp;28,1,1;4&amp;30,1,1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>4&amp;10,4,1;4&amp;12,3,1;4&amp;14,2,1;4&amp;16,2,1;4&amp;18,1,1;4&amp;20,1,1;4&amp;22,1,1;4&amp;24,1,1;4&amp;26,1,1;4&amp;28,1,1;4&amp;30,1,1</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -1113,8 +1118,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.75" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="4" width="13.875" customWidth="1"/>
+    <col min="3" max="3" width="6.75" customWidth="1"/>
+    <col min="4" max="4" width="41.125" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="53.5" customWidth="1"/>
     <col min="7" max="7" width="16.5" customWidth="1"/>
@@ -1162,7 +1167,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
@@ -1227,7 +1232,7 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>65</v>
@@ -1250,7 +1255,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
@@ -1273,7 +1278,7 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>13</v>
@@ -1296,7 +1301,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>14</v>
@@ -1365,7 +1370,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>16</v>
@@ -1383,7 +1388,7 @@
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -1403,7 +1408,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -1423,7 +1428,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -1443,7 +1448,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -1461,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -1481,7 +1486,7 @@
         <v>6</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1501,7 +1506,7 @@
         <v>19</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -1521,7 +1526,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>

--- a/slots/resources/sample/SpecialAuxiliaryAward.xlsx
+++ b/slots/resources/sample/SpecialAuxiliaryAward.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB77A7A-4FA5-4B66-A102-3BC89687D037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A37B16-2D81-471E-B81F-9A52103625C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/slots/resources/sample/SpecialAuxiliaryAward.xlsx
+++ b/slots/resources/sample/SpecialAuxiliaryAward.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A37B16-2D81-471E-B81F-9A52103625C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9451942-53FC-49F8-8BE8-46A825DEBF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliaryAward" sheetId="1" r:id="rId1"/>
@@ -387,7 +387,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="84">
   <si>
     <t>辅助ID</t>
   </si>
@@ -648,27 +648,15 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP1&amp;100100101,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP2&amp;100100102,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP3&amp;100100103,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1;JP4&amp;100100104,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>4&amp;0,2,1;4&amp;10,4,1;4&amp;12,3,1;4&amp;14,2,1;4&amp;16,2,1;4&amp;18,1,1;4&amp;20,1,1;4&amp;22,1,1;4&amp;24,1,1;4&amp;26,1,1;4&amp;28,1,1;4&amp;30,1,1</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>4&amp;10,4,1;4&amp;12,3,1;4&amp;14,2,1;4&amp;16,2,1;4&amp;18,1,1;4&amp;20,1,1;4&amp;22,1,1;4&amp;24,1,1;4&amp;26,1,1;4&amp;28,1,1;4&amp;30,1,1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -1232,7 +1220,7 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>65</v>
@@ -1255,7 +1243,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
@@ -1301,7 +1289,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>14</v>
@@ -1324,7 +1312,7 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>15</v>
@@ -1347,7 +1335,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>15</v>
@@ -1370,7 +1358,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>16</v>

--- a/slots/resources/sample/SpecialAuxiliaryAward.xlsx
+++ b/slots/resources/sample/SpecialAuxiliaryAward.xlsx
@@ -1,40 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9451942-53FC-49F8-8BE8-46A825DEBF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliaryAward" sheetId="1" r:id="rId1"/>
     <sheet name="desc" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>vidisJW</author>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">vidisJW:
@@ -44,21 +50,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>规则以游戏ID*10000为起点</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="C1" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="10"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.Mo:
@@ -68,7 +72,6 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">1.倍率系数：拥有倍率系数时，在该奖励局的免费旋转里面使用每局总奖金 = 旋转总奖金X倍率系数（系数在该奖励局开始前确定，后面则直接使用该数值）
@@ -84,7 +87,6 @@
             <b/>
             <sz val="10"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>结果倍率增加</t>
@@ -93,7 +95,6 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">，翻倍乘数累加（默认送1倍，如果这里再填了1倍，则进入免费游戏后，翻倍乘数为2倍）
@@ -104,7 +105,6 @@
             <b/>
             <sz val="10"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>结果倍率设置</t>
@@ -113,7 +113,6 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">，翻倍乘数每次比较后，取最大值
@@ -124,7 +123,6 @@
             <b/>
             <sz val="10"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>触发自定义事件</t>
@@ -133,14 +131,13 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>，自定义逻辑触发事件条件</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="D1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -148,7 +145,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Mr.Mo:  跟次数相关
@@ -159,7 +155,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">，格式：[{倍率, 权重}]   例子[{10,10},{20,5},{30,2}]
@@ -171,7 +166,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>递增加倍系数</t>
@@ -181,7 +175,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">，格式：[{递增系数, 权重}]   例[{1,10}]
@@ -193,7 +186,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>加倍系数</t>
@@ -203,7 +195,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">，格式：[{元素，数量, 加倍}]   例[{A,0,-3},{A,1,2},{A,2,4},{A,3,6},{A,4,6},{A,5,6},{A,6,6},{A,7,6}]
@@ -215,7 +206,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>随机赖子</t>
@@ -225,7 +215,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">，格式：[{元素，权重}， {元素，权重}]  例[{10,5},{J,5},{Q,5}]
@@ -237,7 +226,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>滚轴</t>
@@ -247,7 +235,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">，格式：[{滚轴ID, 权重}]  例[{3,10]}
@@ -259,7 +246,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>固定元素位置</t>
@@ -269,7 +255,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">，格式：[{元素， 位置},{元素，位置}] 例[{11,2},{11,5}]
@@ -281,7 +266,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>免费次数</t>
@@ -291,14 +275,13 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>，格式：[{免费次数,权重,出现次数},{免费次数,权重,出现次数}]</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="E1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -306,7 +289,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Mr.Mo:   跟元素ID相关
@@ -317,7 +299,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>，格式：[{倍率, 权重}]，例子[{10,10},{20,5},{30,2}]
@@ -329,14 +310,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="F1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="12"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>类型
@@ -352,7 +332,6 @@
             <sz val="18"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>}总贡献值倍数除以100
@@ -363,7 +342,6 @@
             <sz val="12"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>类型值&amp;倍数,权重,抽取次数最大值</t>
@@ -374,7 +352,6 @@
             <sz val="18"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -387,11 +364,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="124">
   <si>
     <t>辅助ID</t>
   </si>
   <si>
+    <t>游戏类型</t>
+  </si>
+  <si>
     <t>类型</t>
   </si>
   <si>
@@ -410,12 +390,21 @@
     <t>int</t>
   </si>
   <si>
+    <t>List&lt;List&lt;int&gt;{,}&gt;{;}</t>
+  </si>
+  <si>
     <t>String</t>
   </si>
   <si>
+    <t>List&lt;String&gt;{;}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
+    <t>gameType</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -425,39 +414,201 @@
     <t>awardTypeB</t>
   </si>
   <si>
+    <t>awardTypeC</t>
+  </si>
+  <si>
+    <t>2&amp;2,200,1;2&amp;3,500,1;2&amp;5,2500,1;2&amp;8,1200,1;2&amp;10,1000,1;2&amp;12,1000,1;2&amp;15,800,1;2&amp;18,200,1;2&amp;20,100,1;2&amp;25,50,1;2&amp;30,10,1</t>
+  </si>
+  <si>
+    <t>拉火车绿火车MINI</t>
+  </si>
+  <si>
+    <t>2&amp;2,1000,1;2&amp;3,1000,1;2&amp;5,2500,1;2&amp;8,1200,1;2&amp;10,900,1;2&amp;12,800,1;2&amp;15,300,1;2&amp;18,50,1;2&amp;20,5,1;2&amp;25,0,1;2&amp;30,0,1</t>
+  </si>
+  <si>
     <t>拉火车蓝火车MINOR</t>
   </si>
   <si>
+    <t>2&amp;2,1000,1;2&amp;3,1000,1;2&amp;5,2500,1;2&amp;8,1000,1;2&amp;10,800,1;2&amp;12,500,1;2&amp;15,10,1;2&amp;18,5,1;2&amp;20,1,1;2&amp;25,0,1;2&amp;30,0,1</t>
+  </si>
+  <si>
     <t>拉火车紫火车MAJOR</t>
   </si>
   <si>
+    <t>2&amp;2,1500,1;2&amp;3,1200,1;2&amp;5,1200,1;2&amp;8,1000,1;2&amp;10,800,1;2&amp;12,150,1;2&amp;15,50,1;2&amp;18,1,1;2&amp;20,0,1;2&amp;25,0,1;2&amp;30,0,1</t>
+  </si>
+  <si>
     <t>拉火车红火车GRAND</t>
   </si>
   <si>
+    <t>4&amp;0,800,1;4&amp;2,1000,1;4&amp;3,1000,1;4&amp;5,2500,1;4&amp;8,1200,1;4&amp;10,900,1;4&amp;12,800,1;4&amp;15,300,1;4&amp;18,50,1;4&amp;20,5,1;4&amp;25,0,1;4&amp;30,0,1</t>
+  </si>
+  <si>
     <t>存在金币为0</t>
   </si>
   <si>
+    <t>4&amp;0,900,1;4&amp;2,800,1;4&amp;3,800,1;4&amp;5,2500,1;4&amp;8,1200,1;4&amp;10,900,1;4&amp;12,800,1;4&amp;15,300,1;4&amp;18,50,1;4&amp;20,5,1;4&amp;25,0,1;4&amp;30,0,1</t>
+  </si>
+  <si>
+    <t>4&amp;2,1000,1;4&amp;3,1000,1;4&amp;5,2500,1;4&amp;8,1200,1;4&amp;10,900,1;4&amp;12,800,1;4&amp;15,300,1;4&amp;18,50,1;4&amp;20,5,1;4&amp;25,1,1;2&amp;30,0,1</t>
+  </si>
+  <si>
     <t>存在金币非0</t>
   </si>
   <si>
+    <t>4,1,1;5,3,1;6,10,1;7,20,1;8,18,1;9,15,1;10,10,1;11,5,1;12,3,1</t>
+  </si>
+  <si>
     <t>黄金火车奖励翻几倍</t>
   </si>
   <si>
+    <t>10010010,1,1</t>
+  </si>
+  <si>
     <t>选择拉火车</t>
   </si>
   <si>
+    <t>10010008,1,1</t>
+  </si>
+  <si>
     <t>免费转</t>
   </si>
   <si>
+    <t>10010009,1,1</t>
+  </si>
+  <si>
+    <t>小游戏选黄金列车</t>
+  </si>
+  <si>
+    <t>8,1,1</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>2,1,1</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
+  </si>
+  <si>
     <t>地图全解锁送黄金列车，转出触发局</t>
   </si>
   <si>
+    <t>3,1,1</t>
+  </si>
+  <si>
     <t>触发局所用滚轴</t>
   </si>
   <si>
+    <t>4,1,1;5,3,1;6,15,1;7,18,1;8,10,1;9,7,1;10,5,1;11,1,1;12,1,1</t>
+  </si>
+  <si>
+    <t>4,1,1;5,3,1;6,20,1;7,15,1;8,10,1;9,7,1;10,5,1;11,1,1;12,0,1</t>
+  </si>
+  <si>
+    <t>4,1,1;5,3,1;6,20,1;7,15,1;8,10,1;9,5,1;10,5,1;11,1,1;12,1,1</t>
+  </si>
+  <si>
+    <t>4,1,1;5,6,1;6,20,1;7,15,1;8,10,1;9,5,1;10,3,1;11,0,1;12,0,1</t>
+  </si>
+  <si>
+    <t>4,1,1;5,18,1;6,15,1;7,12,1;8,8,1;9,4,1;10,1,1;11,0,1;12,0,1</t>
+  </si>
+  <si>
+    <t>10010024,1,1</t>
+  </si>
+  <si>
+    <t>10010025,1,1</t>
+  </si>
+  <si>
+    <t>10010026,1,1</t>
+  </si>
+  <si>
+    <t>10010027,1,1</t>
+  </si>
+  <si>
+    <t>10010028,1,1</t>
+  </si>
+  <si>
+    <t>10010029,1,1</t>
+  </si>
+  <si>
+    <t>10010042,1,1</t>
+  </si>
+  <si>
+    <t>10010043,1,1</t>
+  </si>
+  <si>
+    <t>10010044,1,1</t>
+  </si>
+  <si>
+    <t>10010045,1,1</t>
+  </si>
+  <si>
+    <t>10010046,1,1</t>
+  </si>
+  <si>
+    <t>10010047,1,1</t>
+  </si>
+  <si>
+    <t>5,1,1</t>
+  </si>
+  <si>
+    <t>免费滚轴</t>
+  </si>
+  <si>
+    <t>11,1,1</t>
+  </si>
+  <si>
+    <t>14,1,1</t>
+  </si>
+  <si>
+    <t>17,1,1</t>
+  </si>
+  <si>
+    <t>20,1,1</t>
+  </si>
+  <si>
+    <t>10010036,1,1</t>
+  </si>
+  <si>
+    <t>10010037,1,1</t>
+  </si>
+  <si>
+    <t>10010038,1,1</t>
+  </si>
+  <si>
+    <t>10010039,1,1</t>
+  </si>
+  <si>
+    <t>10010040,1,1</t>
+  </si>
+  <si>
+    <t>10010041,1,1</t>
+  </si>
+  <si>
+    <t>6,1,1</t>
+  </si>
+  <si>
+    <t>重转转一局触发局所用滚轴</t>
+  </si>
+  <si>
+    <t>9,1,1</t>
+  </si>
+  <si>
+    <t>12,1,1</t>
+  </si>
+  <si>
+    <t>15,1,1</t>
+  </si>
+  <si>
+    <t>18,1,1</t>
+  </si>
+  <si>
+    <t>21,1,1</t>
+  </si>
+  <si>
     <t>typeID</t>
   </si>
   <si>
@@ -575,6 +726,9 @@
     <t>&lt;!--小游戏选中该事件后，结束小游戏，并奖励相应金币系数--&gt;</t>
   </si>
   <si>
+    <t>奖励小游戏</t>
+  </si>
+  <si>
     <t>&lt;!--小游戏里面再触发另一个小游戏--&gt;</t>
   </si>
   <si>
@@ -582,93 +736,21 @@
   </si>
   <si>
     <t>&lt;!--在某事件后，触发免费重转，与普通重转不一样，如破冰--&gt;</t>
-  </si>
-  <si>
-    <t>拉火车绿火车MINI</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;String&gt;{;}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏类型</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>gameType</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>awardTypeC</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>奖励小游戏</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,1,1;3,1,1;4,1,1;5,1,1;6,1,1;7,1,1;8,1,1;9,1,1;10,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;List&lt;int&gt;{,}&gt;{;}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>10010010,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>10010008,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>8,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>10010009,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>4&amp;0,2,1;4&amp;10,4,1;4&amp;12,3,1;4&amp;14,2,1;4&amp;16,2,1;4&amp;18,1,1;4&amp;20,1,1;4&amp;22,1,1;4&amp;24,1,1;4&amp;26,1,1;4&amp;28,1,1;4&amp;30,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>4&amp;10,4,1;4&amp;12,3,1;4&amp;14,2,1;4&amp;16,2,1;4&amp;18,1,1;4&amp;20,1,1;4&amp;22,1,1;4&amp;24,1,1;4&amp;26,1,1;4&amp;28,1,1;4&amp;30,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2&amp;8,2,1;2&amp;10,4,1;2&amp;12,3,1;2&amp;14,2,1;2&amp;16,2,1;2&amp;18,1,1;2&amp;20,1,1;2&amp;22,1,1;2&amp;24,1,1;2&amp;26,1,1;2&amp;28,1,1;2&amp;30,1,1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -680,41 +762,210 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -722,70 +973,204 @@
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -793,10 +1178,252 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -812,15 +1439,63 @@
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
+          <bgColor theme="8" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
@@ -830,18 +1505,8 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1096,14 +1761,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="12.75" customWidth="1"/>
     <col min="3" max="3" width="6.75" customWidth="1"/>
@@ -1117,51 +1782,51 @@
     <col min="11" max="11" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" ht="16.5" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" ht="16.5" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="2"/>
@@ -1169,24 +1834,24 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="3" ht="16.5" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="2"/>
@@ -1194,7 +1859,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="4" ht="16.5" spans="1:11">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1207,7 +1872,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="5" ht="16.5" spans="1:11">
       <c r="A5" s="1">
         <v>1001000101</v>
       </c>
@@ -1220,17 +1885,17 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="6" ht="16.5" spans="1:11">
       <c r="A6" s="1">
         <v>1001000201</v>
       </c>
@@ -1243,17 +1908,17 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="7" ht="16.5" spans="1:11">
       <c r="A7" s="1">
         <v>1001000301</v>
       </c>
@@ -1266,17 +1931,17 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="8" ht="16.5" spans="1:11">
       <c r="A8" s="1">
         <v>1001000401</v>
       </c>
@@ -1289,17 +1954,17 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="9" ht="16.5" spans="1:11">
       <c r="A9" s="1">
         <v>1001000501</v>
       </c>
@@ -1312,17 +1977,17 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="10" ht="16.5" spans="1:11">
       <c r="A10" s="1">
         <v>1001000502</v>
       </c>
@@ -1335,17 +2000,17 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="11" ht="16.5" spans="1:8">
       <c r="A11" s="1">
         <v>1001000503</v>
       </c>
@@ -1358,14 +2023,14 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="12" ht="16.5" spans="1:8">
       <c r="A12" s="1">
         <v>1001000504</v>
       </c>
@@ -1376,16 +2041,16 @@
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="13" ht="16.5" spans="1:8">
       <c r="A13" s="1">
         <v>1001000701</v>
       </c>
@@ -1396,16 +2061,16 @@
         <v>18</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="14" ht="16.5" spans="1:8">
       <c r="A14" s="1">
         <v>1001000702</v>
       </c>
@@ -1416,16 +2081,16 @@
         <v>18</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="15" ht="16.5" spans="1:8">
       <c r="A15" s="1">
         <v>1001000703</v>
       </c>
@@ -1436,14 +2101,16 @@
         <v>18</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="16" ht="16.5" spans="1:8">
       <c r="A16" s="1">
         <v>1001000801</v>
       </c>
@@ -1454,16 +2121,16 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="17" ht="16.5" spans="1:8">
       <c r="A17" s="1">
         <v>1001000802</v>
       </c>
@@ -1474,16 +2141,16 @@
         <v>6</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="18" ht="16.5" spans="1:8">
       <c r="A18" s="1">
         <v>1001000901</v>
       </c>
@@ -1494,16 +2161,16 @@
         <v>19</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="19" ht="16.5" spans="1:8">
       <c r="A19" s="1">
         <v>1001000902</v>
       </c>
@@ -1514,31 +2181,753 @@
         <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H19" s="5"/>
     </row>
+    <row r="20" ht="16.5" spans="1:8">
+      <c r="A20" s="1">
+        <v>1001000505</v>
+      </c>
+      <c r="B20" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C20" s="1">
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:8">
+      <c r="A21" s="1">
+        <v>1001000506</v>
+      </c>
+      <c r="B21" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:8">
+      <c r="A22" s="1">
+        <v>1001000507</v>
+      </c>
+      <c r="B22" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C22" s="1">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:8">
+      <c r="A23" s="1">
+        <v>1001000508</v>
+      </c>
+      <c r="B23" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C23" s="1">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:8">
+      <c r="A24" s="1">
+        <v>1001000509</v>
+      </c>
+      <c r="B24" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C24" s="1">
+        <v>16</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:8">
+      <c r="A25" s="1">
+        <v>1001000510</v>
+      </c>
+      <c r="B25" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C25" s="1">
+        <v>16</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:8">
+      <c r="A26" s="1">
+        <v>1001000704</v>
+      </c>
+      <c r="B26" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C26" s="1">
+        <v>18</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:8">
+      <c r="A27" s="1">
+        <v>1001000705</v>
+      </c>
+      <c r="B27" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C27" s="1">
+        <v>18</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:8">
+      <c r="A28" s="1">
+        <v>1001000706</v>
+      </c>
+      <c r="B28" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C28" s="1">
+        <v>18</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:8">
+      <c r="A29" s="1">
+        <v>1001000707</v>
+      </c>
+      <c r="B29" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C29" s="1">
+        <v>18</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:8">
+      <c r="A30" s="1">
+        <v>1001000708</v>
+      </c>
+      <c r="B30" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C30" s="1">
+        <v>18</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:8">
+      <c r="A31" s="1">
+        <v>1001000709</v>
+      </c>
+      <c r="B31" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C31" s="1">
+        <v>18</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:7">
+      <c r="A32" s="1">
+        <v>1001000710</v>
+      </c>
+      <c r="B32" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C32" s="1">
+        <v>18</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:7">
+      <c r="A33" s="1">
+        <v>1001000711</v>
+      </c>
+      <c r="B33" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C33" s="1">
+        <v>18</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:7">
+      <c r="A34" s="1">
+        <v>1001000712</v>
+      </c>
+      <c r="B34" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C34" s="1">
+        <v>18</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:7">
+      <c r="A35" s="1">
+        <v>1001000713</v>
+      </c>
+      <c r="B35" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C35" s="1">
+        <v>18</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="1:7">
+      <c r="A36" s="1">
+        <v>1001000714</v>
+      </c>
+      <c r="B36" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C36" s="1">
+        <v>18</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="1:7">
+      <c r="A37" s="1">
+        <v>1001000715</v>
+      </c>
+      <c r="B37" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C37" s="1">
+        <v>18</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:7">
+      <c r="A38" s="1">
+        <v>1001000803</v>
+      </c>
+      <c r="B38" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C38" s="1">
+        <v>6</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:7">
+      <c r="A39" s="1">
+        <v>1001000804</v>
+      </c>
+      <c r="B39" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C39" s="1">
+        <v>6</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="1:7">
+      <c r="A40" s="1">
+        <v>1001000805</v>
+      </c>
+      <c r="B40" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C40" s="1">
+        <v>6</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:7">
+      <c r="A41" s="1">
+        <v>1001000806</v>
+      </c>
+      <c r="B41" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C41" s="1">
+        <v>6</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:7">
+      <c r="A42" s="1">
+        <v>1001000807</v>
+      </c>
+      <c r="B42" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C42" s="1">
+        <v>6</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:7">
+      <c r="A43" s="1">
+        <v>1001000808</v>
+      </c>
+      <c r="B43" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C43" s="1">
+        <v>6</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:7">
+      <c r="A44" s="1">
+        <v>1001000716</v>
+      </c>
+      <c r="B44" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C44" s="1">
+        <v>18</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:7">
+      <c r="A45" s="1">
+        <v>1001000717</v>
+      </c>
+      <c r="B45" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C45" s="1">
+        <v>18</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:7">
+      <c r="A46" s="1">
+        <v>1001000718</v>
+      </c>
+      <c r="B46" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C46" s="1">
+        <v>18</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:7">
+      <c r="A47" s="1">
+        <v>1001000719</v>
+      </c>
+      <c r="B47" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C47" s="1">
+        <v>18</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:7">
+      <c r="A48" s="1">
+        <v>1001000720</v>
+      </c>
+      <c r="B48" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C48" s="1">
+        <v>18</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:7">
+      <c r="A49" s="1">
+        <v>1001000721</v>
+      </c>
+      <c r="B49" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C49" s="1">
+        <v>18</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:7">
+      <c r="A50" s="1">
+        <v>1001000903</v>
+      </c>
+      <c r="B50" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C50" s="1">
+        <v>6</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:7">
+      <c r="A51" s="1">
+        <v>1001000904</v>
+      </c>
+      <c r="B51" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C51" s="1">
+        <v>6</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:7">
+      <c r="A52" s="1">
+        <v>1001000905</v>
+      </c>
+      <c r="B52" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C52" s="1">
+        <v>6</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:7">
+      <c r="A53" s="1">
+        <v>1001000906</v>
+      </c>
+      <c r="B53" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C53" s="1">
+        <v>6</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:7">
+      <c r="A54" s="1">
+        <v>1001000907</v>
+      </c>
+      <c r="B54" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C54" s="1">
+        <v>6</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:7">
+      <c r="A55" s="1">
+        <v>1001000908</v>
+      </c>
+      <c r="B55" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C55" s="1">
+        <v>6</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="A1:G4 D5:D11 E5:E19">
+  <conditionalFormatting sqref="E26:E31">
     <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD(MID($A26,1,4),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E32:E37">
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>MOD(MID($A32,1,4),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E38:E43">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>MOD(MID($A38,1,4),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E44:E49">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>MOD(MID($A44,1,4),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E50:E55">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD(MID($A50,1,4),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:G4 D5:E11 E12:E25">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>MOD(MID($A1,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.75" customWidth="1"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
@@ -1553,15 +2942,15 @@
     <col min="13" max="13" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" ht="16.5" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1572,15 +2961,15 @@
       <c r="J1" s="2"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -1590,15 +2979,15 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="3" ht="16.5" spans="1:13">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1607,227 +2996,227 @@
       <c r="H3" s="2"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="H4"/>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="J5"/>
     </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="H6"/>
     </row>
-    <row r="7" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="H7"/>
     </row>
-    <row r="8" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="H8"/>
     </row>
-    <row r="9" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:4">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="D9"/>
     </row>
-    <row r="10" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="H10"/>
     </row>
-    <row r="11" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="H11"/>
     </row>
-    <row r="12" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="H12"/>
     </row>
-    <row r="13" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="H13"/>
     </row>
-    <row r="14" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="H14"/>
     </row>
-    <row r="15" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="H15"/>
     </row>
-    <row r="16" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="H16"/>
     </row>
-    <row r="17" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="H17"/>
     </row>
-    <row r="18" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="H18"/>
     </row>
-    <row r="19" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="19" s="1" customFormat="1" ht="16.5" spans="1:7">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="G19"/>
     </row>
-    <row r="20" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="20" s="1" customFormat="1" ht="16.5" spans="1:7">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="G20"/>
     </row>
-    <row r="21" spans="1:8" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="21" s="1" customFormat="1" ht="16.5" spans="1:7">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="G21"/>
     </row>
-    <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="22" ht="16.5" spans="1:1">
       <c r="A22" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialAuxiliaryAward.xlsx
+++ b/slots/resources/sample/SpecialAuxiliaryAward.xlsx
@@ -364,7 +364,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="123">
   <si>
     <t>辅助ID</t>
   </si>
@@ -417,7 +417,7 @@
     <t>awardTypeC</t>
   </si>
   <si>
-    <t>2&amp;2,200,1;2&amp;3,500,1;2&amp;5,2500,1;2&amp;8,1200,1;2&amp;10,1000,1;2&amp;12,1000,1;2&amp;15,800,1;2&amp;18,200,1;2&amp;20,100,1;2&amp;25,50,1;2&amp;30,10,1</t>
+    <t>2&amp;2,200,1;2&amp;3,500,1;2&amp;5,2500,1;2&amp;8,1200,1;2&amp;10,1000,1;2&amp;12,1000,1;2&amp;15,800,1;2&amp;18,200,1;2&amp;20,100,1;2&amp;25,50,1;2&amp;30,10,1;2&amp;40,1,1</t>
   </si>
   <si>
     <t>拉火车绿火车MINI</t>
@@ -456,7 +456,7 @@
     <t>存在金币非0</t>
   </si>
   <si>
-    <t>4,1,1;5,3,1;6,10,1;7,20,1;8,18,1;9,15,1;10,10,1;11,5,1;12,3,1</t>
+    <t>4,0,1;5,1,1;6,3,1;7,15,1;8,15,1;9,8,1;10,3,1;11,1,1</t>
   </si>
   <si>
     <t>黄金火车奖励翻几倍</t>
@@ -501,19 +501,16 @@
     <t>触发局所用滚轴</t>
   </si>
   <si>
-    <t>4,1,1;5,3,1;6,15,1;7,18,1;8,10,1;9,7,1;10,5,1;11,1,1;12,1,1</t>
-  </si>
-  <si>
-    <t>4,1,1;5,3,1;6,20,1;7,15,1;8,10,1;9,7,1;10,5,1;11,1,1;12,0,1</t>
-  </si>
-  <si>
-    <t>4,1,1;5,3,1;6,20,1;7,15,1;8,10,1;9,5,1;10,5,1;11,1,1;12,1,1</t>
-  </si>
-  <si>
-    <t>4,1,1;5,6,1;6,20,1;7,15,1;8,10,1;9,5,1;10,3,1;11,0,1;12,0,1</t>
-  </si>
-  <si>
-    <t>4,1,1;5,18,1;6,15,1;7,12,1;8,8,1;9,4,1;10,1,1;11,0,1;12,0,1</t>
+    <t>4,5,1;5,15,1;6,10,1;7,5,1;8,1,1</t>
+  </si>
+  <si>
+    <t>4,5,1;5,15,1;6,1,1</t>
+  </si>
+  <si>
+    <t>4,3,1;5,8,1;6,1,1</t>
+  </si>
+  <si>
+    <t>4,8,1;5,5,1;6,1,1</t>
   </si>
   <si>
     <t>10010024,1,1</t>
@@ -915,20 +912,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -938,6 +929,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -957,7 +954,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2241,7 +2238,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -2261,7 +2258,7 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -2301,7 +2298,7 @@
         <v>16</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -2321,7 +2318,7 @@
         <v>18</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -2341,7 +2338,7 @@
         <v>18</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -2361,7 +2358,7 @@
         <v>18</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -2381,7 +2378,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -2401,7 +2398,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -2421,7 +2418,7 @@
         <v>18</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -2441,7 +2438,7 @@
         <v>18</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -2460,7 +2457,7 @@
         <v>18</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -2479,7 +2476,7 @@
         <v>18</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -2498,7 +2495,7 @@
         <v>18</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
@@ -2517,7 +2514,7 @@
         <v>18</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -2536,7 +2533,7 @@
         <v>18</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -2555,12 +2552,12 @@
         <v>6</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:7">
@@ -2579,7 +2576,7 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:7">
@@ -2593,12 +2590,12 @@
         <v>6</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:7">
@@ -2612,12 +2609,12 @@
         <v>6</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:7">
@@ -2631,12 +2628,12 @@
         <v>6</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:7">
@@ -2650,12 +2647,12 @@
         <v>6</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:7">
@@ -2669,7 +2666,7 @@
         <v>18</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -2688,7 +2685,7 @@
         <v>18</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -2707,7 +2704,7 @@
         <v>18</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -2726,7 +2723,7 @@
         <v>18</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -2745,7 +2742,7 @@
         <v>18</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -2764,7 +2761,7 @@
         <v>18</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -2783,12 +2780,12 @@
         <v>6</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:7">
@@ -2802,12 +2799,12 @@
         <v>6</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:7">
@@ -2821,12 +2818,12 @@
         <v>6</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:7">
@@ -2840,12 +2837,12 @@
         <v>6</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:7">
@@ -2859,12 +2856,12 @@
         <v>6</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:7">
@@ -2878,12 +2875,12 @@
         <v>6</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2944,13 +2941,13 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:13">
       <c r="A1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -2966,10 +2963,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -2984,10 +2981,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -3001,10 +2998,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="H4"/>
     </row>
@@ -3013,10 +3010,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="J5"/>
     </row>
@@ -3025,10 +3022,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="H6"/>
     </row>
@@ -3037,10 +3034,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="H7"/>
     </row>
@@ -3049,10 +3046,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="H8"/>
     </row>
@@ -3061,10 +3058,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="D9"/>
     </row>
@@ -3073,10 +3070,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="H10"/>
     </row>
@@ -3085,10 +3082,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="H11"/>
     </row>
@@ -3097,10 +3094,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="H12"/>
     </row>
@@ -3109,10 +3106,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="H13"/>
     </row>
@@ -3121,10 +3118,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="H14"/>
     </row>
@@ -3133,10 +3130,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="H15"/>
     </row>
@@ -3145,10 +3142,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="H16"/>
     </row>
@@ -3157,10 +3154,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="H17"/>
     </row>
@@ -3169,10 +3166,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="H18"/>
     </row>
@@ -3181,10 +3178,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="G19"/>
     </row>
@@ -3193,10 +3190,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="G20"/>
     </row>
@@ -3205,10 +3202,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="G21"/>
     </row>
